--- a/docs/downloads/13/tbl_synthese_qualite_alaotra_avaradrano.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_alaotra_avaradrano.xlsx
@@ -392,9 +392,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -412,9 +409,6 @@
           <t>Neutre</t>
         </is>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -452,9 +446,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -511,9 +502,6 @@
         <is>
           <t>Mefiant</t>
         </is>
-      </c>
-      <c r="D8">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
